--- a/Extracted_data_analysis/polar/Output-Transformed_data/summary_counts_question_1-3.xlsx
+++ b/Extracted_data_analysis/polar/Output-Transformed_data/summary_counts_question_1-3.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t xml:space="preserve">meso_substrate</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t xml:space="preserve">Abundance+Density+Diversity+Habitat+Trophic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abundance+Density+Diversity+Trophic</t>
   </si>
   <si>
     <t xml:space="preserve">Abundance+Density+Habitat</t>
@@ -570,10 +573,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="3">
@@ -584,7 +587,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="4">
@@ -595,7 +598,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="5">
@@ -606,7 +609,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
     </row>
   </sheetData>
@@ -636,10 +639,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>58.62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -650,7 +653,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>24.14</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="4">
@@ -661,7 +664,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
     </row>
   </sheetData>
@@ -694,7 +697,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="3">
@@ -705,7 +708,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -716,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="5">
@@ -727,7 +730,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="6">
@@ -735,10 +738,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>62.07</v>
+        <v>63.33</v>
       </c>
     </row>
     <row r="7">
@@ -749,7 +752,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="8">
@@ -760,7 +763,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="9">
@@ -771,7 +774,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>
@@ -804,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="3">
@@ -812,10 +815,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
     </row>
   </sheetData>
@@ -845,10 +848,10 @@
         <v>22</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>41.38</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="3">
@@ -859,7 +862,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>13.79</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="4">
@@ -870,7 +873,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="5">
@@ -881,7 +884,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -892,7 +895,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +928,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="3">
@@ -936,7 +939,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="4">
@@ -947,7 +950,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="5">
@@ -958,7 +961,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="6">
@@ -969,7 +972,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="7">
@@ -980,7 +983,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="8">
@@ -991,7 +994,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="9">
@@ -1002,7 +1005,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="10">
@@ -1013,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="11">
@@ -1024,7 +1027,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="12">
@@ -1035,7 +1038,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="13">
@@ -1043,10 +1046,10 @@
         <v>39</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>6.9</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="14">
@@ -1054,10 +1057,10 @@
         <v>40</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>10.34</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="15">
@@ -1065,10 +1068,10 @@
         <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>3.45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -1079,7 +1082,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="17">
@@ -1090,7 +1093,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="18">
@@ -1101,7 +1104,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="19">
@@ -1112,7 +1115,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="20">
@@ -1123,7 +1126,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="21">
@@ -1134,7 +1137,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="22">
@@ -1145,7 +1148,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="23">
@@ -1156,7 +1159,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="24">
@@ -1167,7 +1170,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="25">
@@ -1178,7 +1181,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="26">
@@ -1189,7 +1192,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="27">
@@ -1200,7 +1203,18 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>
@@ -1216,7 +1230,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1227,112 +1241,112 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" t="n">
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>13.79</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" t="n">
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B9" t="n">
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.03</v>
+        <v>33.33</v>
       </c>
     </row>
   </sheetData>
@@ -1348,7 +1362,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1359,35 +1373,35 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>93.1</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>
